--- a/artfynd/A 37011-2025 artfynd.xlsx
+++ b/artfynd/A 37011-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415009</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37011-2025 artfynd.xlsx
+++ b/artfynd/A 37011-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415009</v>
       </c>
       <c r="B2" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37011-2025 artfynd.xlsx
+++ b/artfynd/A 37011-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415009</v>
       </c>
       <c r="B2" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37011-2025 artfynd.xlsx
+++ b/artfynd/A 37011-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415009</v>
       </c>
       <c r="B2" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37011-2025 artfynd.xlsx
+++ b/artfynd/A 37011-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415009</v>
       </c>
       <c r="B2" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37011-2025 artfynd.xlsx
+++ b/artfynd/A 37011-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415009</v>
       </c>
       <c r="B2" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37011-2025 artfynd.xlsx
+++ b/artfynd/A 37011-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415009</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37011-2025 artfynd.xlsx
+++ b/artfynd/A 37011-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415009</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37011-2025 artfynd.xlsx
+++ b/artfynd/A 37011-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415009</v>
       </c>
       <c r="B2" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37011-2025 artfynd.xlsx
+++ b/artfynd/A 37011-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,6 +778,360 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128806217</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Söderåsens naturreservat, Söderåsens naturreservat, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>576500</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6708247</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fanns utanför naturreservatet, en bit bort från gränsen</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Stephen Hinton</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Stephen Hinton</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128806150</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Söderåsens naturreservat, Söderåsens naturreservat, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>576508</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6708244</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Maj-Lis Koivisto</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Maj-Lis Koivisto</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128805882</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Söderåsens naturreservat, Söderåsens naturreservat, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>576439</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6708247</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Maj-Lis Koivisto</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Maj-Lis Koivisto</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37011-2025 artfynd.xlsx
+++ b/artfynd/A 37011-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128806217</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>128806150</v>
       </c>
       <c r="B4" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128805882</v>
       </c>
       <c r="B5" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37011-2025 artfynd.xlsx
+++ b/artfynd/A 37011-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128806217</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>128806150</v>
       </c>
       <c r="B4" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128805882</v>
       </c>
       <c r="B5" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37011-2025 artfynd.xlsx
+++ b/artfynd/A 37011-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128806217</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>128806150</v>
       </c>
       <c r="B4" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128805882</v>
       </c>
       <c r="B5" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37011-2025 artfynd.xlsx
+++ b/artfynd/A 37011-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128806217</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>128806150</v>
       </c>
       <c r="B4" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128805882</v>
       </c>
       <c r="B5" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37011-2025 artfynd.xlsx
+++ b/artfynd/A 37011-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128806217</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>128806150</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128805882</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37011-2025 artfynd.xlsx
+++ b/artfynd/A 37011-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128806217</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>128806150</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128805882</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37011-2025 artfynd.xlsx
+++ b/artfynd/A 37011-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128806217</v>
       </c>
       <c r="B3" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>128806150</v>
       </c>
       <c r="B4" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128805882</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37011-2025 artfynd.xlsx
+++ b/artfynd/A 37011-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128806217</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>128806150</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128805882</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37011-2025 artfynd.xlsx
+++ b/artfynd/A 37011-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128806217</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>128806150</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128805882</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37011-2025 artfynd.xlsx
+++ b/artfynd/A 37011-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128806217</v>
       </c>
       <c r="B3" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>128806150</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128805882</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37011-2025 artfynd.xlsx
+++ b/artfynd/A 37011-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128806217</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>128806150</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128805882</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37011-2025 artfynd.xlsx
+++ b/artfynd/A 37011-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128806217</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>128806150</v>
       </c>
       <c r="B4" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128805882</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37011-2025 artfynd.xlsx
+++ b/artfynd/A 37011-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127415009</v>
+        <v>61008293</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjärnäs, Gstr</t>
+          <t>söderåsen, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576491</v>
+        <v>576486</v>
       </c>
       <c r="R2" t="n">
-        <v>6708247</v>
+        <v>6708190</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,17 +746,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2016-08-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2016-08-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,28 +760,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128806217</v>
+        <v>127415009</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,24 +807,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Söderåsens naturreservat, Söderåsens naturreservat, Gstr</t>
+          <t>Tjärnäs, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576500</v>
+        <v>576491</v>
       </c>
       <c r="R3" t="n">
         <v>6708247</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,27 +848,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:11</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:11</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Fanns utanför naturreservatet, en bit bort från gränsen</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,29 +867,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stephen Hinton</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stephen Hinton</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128806150</v>
+        <v>128805882</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,7 +915,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -936,16 +923,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Söderåsens naturreservat, Söderåsens naturreservat, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576508</v>
+        <v>576439</v>
       </c>
       <c r="R4" t="n">
-        <v>6708244</v>
+        <v>6708247</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128805882</v>
+        <v>128806150</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,7 +1036,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1052,21 +1044,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Söderåsens naturreservat, Söderåsens naturreservat, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576439</v>
+        <v>576508</v>
       </c>
       <c r="R5" t="n">
-        <v>6708247</v>
+        <v>6708244</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,6 +1119,123 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128806217</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Söderåsens naturreservat, Söderåsens naturreservat, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>576500</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6708247</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Fanns utanför naturreservatet, en bit bort från gränsen</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Stephen Hinton</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Stephen Hinton</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37011-2025 artfynd.xlsx
+++ b/artfynd/A 37011-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61008293</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127415009</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128805882</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1119,6 +1139,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128806150</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,8 +1261,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128806217</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>